--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBB22DA-EE84-49A6-B624-F28B6FA3C8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510CEE63-69D3-43FD-96B2-647E2E182B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C851EA1D-5267-41B7-9513-D07E5A57DEF2}"/>
   </bookViews>
@@ -13664,8 +13664,8 @@
       <c r="F279" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="G279" s="2" t="s">
-        <v>12</v>
+      <c r="G279" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="H279" s="6" t="s">
         <v>15</v>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095BD1AC-0E62-48C2-BB05-03E368DE60D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8D2974-BC23-4477-9E19-EB7C53141836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C851EA1D-5267-41B7-9513-D07E5A57DEF2}"/>
   </bookViews>
@@ -14546,7 +14546,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="307" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>1406</v>
       </c>
@@ -14578,7 +14578,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="308" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>1327</v>
       </c>
@@ -14610,7 +14610,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="309" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>1328</v>
       </c>
@@ -20050,7 +20050,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="479" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
         <v>768</v>
       </c>
@@ -20082,7 +20082,7 @@
         <v>179.995</v>
       </c>
     </row>
-    <row r="480" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
         <v>769</v>
       </c>
@@ -20498,7 +20498,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="493" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
         <v>778</v>
       </c>
@@ -20530,7 +20530,7 @@
         <v>179.995</v>
       </c>
     </row>
-    <row r="494" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
         <v>779</v>
       </c>
@@ -24658,7 +24658,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="623" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
         <v>904</v>
       </c>
@@ -24690,7 +24690,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="624" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
         <v>905</v>
       </c>
@@ -24722,7 +24722,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="625" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
         <v>906</v>
       </c>
@@ -24754,7 +24754,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="626" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
         <v>907</v>
       </c>
@@ -24786,7 +24786,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="627" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
         <v>908</v>
       </c>
@@ -26002,7 +26002,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="665" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
         <v>946</v>
       </c>
@@ -26034,7 +26034,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="666" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
         <v>947</v>
       </c>
@@ -27858,7 +27858,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="723" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
         <v>1004</v>
       </c>
@@ -27890,7 +27890,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="724" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
         <v>1005</v>
       </c>
@@ -30450,7 +30450,7 @@
         <v>274.995</v>
       </c>
     </row>
-    <row r="804" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A804" s="2" t="s">
         <v>1085</v>
       </c>
@@ -30482,7 +30482,7 @@
         <v>249.995</v>
       </c>
     </row>
-    <row r="805" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A805" s="2" t="s">
         <v>1087</v>
       </c>
@@ -30514,7 +30514,7 @@
         <v>249.995</v>
       </c>
     </row>
-    <row r="806" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A806" s="2" t="s">
         <v>1088</v>
       </c>
@@ -30546,7 +30546,7 @@
         <v>249.995</v>
       </c>
     </row>
-    <row r="807" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A807" s="2" t="s">
         <v>1089</v>
       </c>
@@ -30578,7 +30578,7 @@
         <v>249.995</v>
       </c>
     </row>
-    <row r="808" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A808" s="2" t="s">
         <v>1090</v>
       </c>
@@ -30610,7 +30610,7 @@
         <v>249.995</v>
       </c>
     </row>
-    <row r="809" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809" s="2" t="s">
         <v>1091</v>
       </c>
@@ -30646,11 +30646,8 @@
   <autoFilter ref="B1:J809" xr:uid="{3A91E150-05DE-47E3-9A71-EF43C5F49301}">
     <filterColumn colId="3">
       <filters>
-        <filter val="CORRE VENTO 3"/>
-        <filter val="JAQUETA CORTA/VENTO CORRE F"/>
-        <filter val="JAQUETA CORTA/VENTO CORRE M"/>
-        <filter val="JAQUETA QUEBRA/VENTO ESSENTIAL F"/>
-        <filter val="JAQUETA QUEBRA/VENTO ESSENTIAL M"/>
+        <filter val="BERMUDA TREINO 7 M"/>
+        <filter val="TREINO"/>
       </filters>
     </filterColumn>
   </autoFilter>
